--- a/temporario/ODP_Luis.xlsx
+++ b/temporario/ODP_Luis.xlsx
@@ -28,6 +28,7 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="14"/>
@@ -35,28 +36,33 @@
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="30"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Times New Roman"/>
+      <family val="1"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="14"/>
       <scheme val="minor"/>
@@ -86,7 +92,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -191,26 +197,6 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
@@ -246,6 +232,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -266,20 +261,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
+      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -322,7 +304,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
@@ -350,14 +332,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -367,11 +341,14 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -381,13 +358,13 @@
     <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -474,7 +451,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>1</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -702,161 +679,166 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col width="24.28515625" customWidth="1" min="1" max="1"/>
-    <col width="19.85546875" customWidth="1" min="2" max="2"/>
-    <col width="14.85546875" customWidth="1" min="3" max="3"/>
-    <col width="17.28515625" customWidth="1" min="4" max="4"/>
-    <col width="17.42578125" customWidth="1" min="5" max="5"/>
-    <col width="19.5703125" customWidth="1" min="6" max="6"/>
-    <col width="29.140625" customWidth="1" min="7" max="7"/>
-    <col width="16.42578125" customWidth="1" min="8" max="8"/>
-    <col width="19.85546875" customWidth="1" min="9" max="9"/>
-    <col width="21.5703125" customWidth="1" min="10" max="10"/>
-    <col width="75.7109375" customWidth="1" min="11" max="11"/>
+    <col width="1.42578125" customWidth="1" min="1" max="1"/>
+    <col width="22.85546875" customWidth="1" min="2" max="2"/>
+    <col width="19.85546875" customWidth="1" min="3" max="3"/>
+    <col width="14.85546875" customWidth="1" min="4" max="4"/>
+    <col width="17.28515625" customWidth="1" min="5" max="5"/>
+    <col width="17.42578125" customWidth="1" min="6" max="6"/>
+    <col width="19.5703125" customWidth="1" min="7" max="7"/>
+    <col width="29.140625" customWidth="1" min="8" max="8"/>
+    <col width="16.42578125" customWidth="1" min="9" max="9"/>
+    <col width="19.85546875" customWidth="1" min="10" max="10"/>
+    <col width="21.5703125" customWidth="1" min="11" max="11"/>
+    <col width="75.7109375" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="12" t="n"/>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="A1" s="18" t="n"/>
+      <c r="B1" s="19" t="n"/>
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>ODP´S DE CADA FUNCIONÁRIO</t>
         </is>
       </c>
-      <c r="C1" s="22" t="n"/>
-      <c r="D1" s="22" t="n"/>
-      <c r="E1" s="22" t="n"/>
-      <c r="F1" s="22" t="n"/>
-      <c r="G1" s="22" t="n"/>
-      <c r="H1" s="22" t="n"/>
-      <c r="I1" s="22" t="n"/>
-      <c r="J1" s="22" t="n"/>
-      <c r="K1" s="23" t="n"/>
+      <c r="D1" s="20" t="n"/>
+      <c r="E1" s="20" t="n"/>
+      <c r="F1" s="20" t="n"/>
+      <c r="G1" s="20" t="n"/>
+      <c r="H1" s="20" t="n"/>
+      <c r="I1" s="20" t="n"/>
+      <c r="J1" s="20" t="n"/>
+      <c r="K1" s="20" t="n"/>
+      <c r="L1" s="19" t="n"/>
     </row>
     <row r="2" ht="58.5" customHeight="1">
-      <c r="A2" s="24" t="n"/>
-      <c r="B2" s="25" t="n"/>
-      <c r="C2" s="26" t="n"/>
-      <c r="D2" s="26" t="n"/>
-      <c r="E2" s="26" t="n"/>
-      <c r="F2" s="26" t="n"/>
-      <c r="G2" s="26" t="n"/>
-      <c r="H2" s="26" t="n"/>
-      <c r="I2" s="26" t="n"/>
-      <c r="J2" s="26" t="n"/>
-      <c r="K2" s="24" t="n"/>
+      <c r="A2" s="21" t="n"/>
+      <c r="B2" s="22" t="n"/>
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="23" t="n"/>
+      <c r="E2" s="23" t="n"/>
+      <c r="F2" s="23" t="n"/>
+      <c r="G2" s="23" t="n"/>
+      <c r="H2" s="23" t="n"/>
+      <c r="I2" s="23" t="n"/>
+      <c r="J2" s="23" t="n"/>
+      <c r="K2" s="23" t="n"/>
+      <c r="L2" s="22" t="n"/>
     </row>
     <row r="3" ht="29.25" customHeight="1">
-      <c r="A3" s="13" t="n"/>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="A3" s="18" t="n"/>
+      <c r="B3" s="19" t="n"/>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>OPERADOR:</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Luis</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>MÁQUINA:</t>
         </is>
       </c>
-      <c r="E3" s="27" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="F3" s="28" t="n"/>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>DATA:</t>
         </is>
       </c>
-      <c r="H3" s="29" t="n">
+      <c r="I3" s="26" t="n">
         <v>46219</v>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>TURNO:</t>
         </is>
       </c>
-      <c r="J3" s="27" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t>Noite</t>
         </is>
       </c>
-      <c r="K3" s="9" t="n"/>
+      <c r="L3" s="9" t="n"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="30" t="n"/>
-      <c r="B4" s="31" t="n"/>
-      <c r="C4" s="32" t="n"/>
-      <c r="D4" s="32" t="n"/>
-      <c r="E4" s="33" t="n"/>
-      <c r="F4" s="34" t="n"/>
-      <c r="G4" s="35" t="n"/>
-      <c r="H4" s="32" t="n"/>
-      <c r="I4" s="32" t="n"/>
-      <c r="J4" s="33" t="n"/>
-      <c r="K4" s="34" t="n"/>
+      <c r="A4" s="27" t="n"/>
+      <c r="B4" s="28" t="n"/>
+      <c r="C4" s="29" t="n"/>
+      <c r="D4" s="30" t="n"/>
+      <c r="E4" s="30" t="n"/>
+      <c r="F4" s="31" t="n"/>
+      <c r="G4" s="32" t="n"/>
+      <c r="H4" s="33" t="n"/>
+      <c r="I4" s="30" t="n"/>
+      <c r="J4" s="30" t="n"/>
+      <c r="K4" s="31" t="n"/>
+      <c r="L4" s="32" t="n"/>
     </row>
     <row r="5" ht="37.5" customHeight="1">
-      <c r="A5" s="36" t="n"/>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="A5" s="21" t="n"/>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>PEDIDO</t>
         </is>
       </c>
-      <c r="C5" s="1" t="inlineStr">
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>OdP</t>
         </is>
       </c>
-      <c r="D5" s="1" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>Nº do PALETE</t>
         </is>
       </c>
-      <c r="E5" s="1" t="inlineStr">
+      <c r="F5" s="1" t="inlineStr">
         <is>
           <t>PESO TOTAL</t>
         </is>
       </c>
-      <c r="F5" s="1" t="inlineStr">
+      <c r="G5" s="1" t="inlineStr">
         <is>
           <t>PESO LÍQUIDO</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
+      <c r="H5" s="1" t="inlineStr">
         <is>
           <t>CLIENTE</t>
         </is>
       </c>
-      <c r="H5" s="1" t="inlineStr">
+      <c r="I5" s="1" t="inlineStr">
         <is>
           <t>PADRÃO</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="J5" s="1" t="inlineStr">
         <is>
           <t>FILME</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>PESO TUBETE</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>OBS</t>
         </is>
       </c>
-      <c r="L5" s="3" t="n"/>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
@@ -866,123 +848,124 @@
       <c r="S5" s="3" t="n"/>
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
-      <c r="V5" s="4" t="n"/>
+      <c r="V5" s="3" t="n"/>
       <c r="W5" s="4" t="n"/>
       <c r="X5" s="4" t="n"/>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n"/>
     </row>
     <row r="6" ht="27" customHeight="1">
-      <c r="B6" s="37" t="inlineStr">
+      <c r="C6" s="34" t="inlineStr">
         <is>
           <t>FAT28210767</t>
         </is>
       </c>
-      <c r="C6" s="37" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>26/02408</t>
         </is>
       </c>
-      <c r="D6" s="37" t="n"/>
-      <c r="E6" s="37" t="n"/>
-      <c r="F6" s="37" t="n"/>
-      <c r="G6" s="37" t="inlineStr">
+      <c r="E6" s="34" t="n"/>
+      <c r="F6" s="34" t="n"/>
+      <c r="G6" s="34" t="n"/>
+      <c r="H6" s="34" t="inlineStr">
         <is>
           <t>IZZAPLAST</t>
         </is>
       </c>
-      <c r="H6" s="37" t="inlineStr">
+      <c r="I6" s="34" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="I6" s="37" t="inlineStr">
+      <c r="J6" s="34" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J6" s="37" t="inlineStr"/>
-      <c r="K6" s="38" t="inlineStr">
+      <c r="K6" s="34" t="inlineStr"/>
+      <c r="L6" s="35" t="inlineStr">
         <is>
           <t>PESAR BOB, POR BOB, PEDIDO DE UNIDADE / SAI CEDO</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="37" t="n">
+      <c r="C8" s="34" t="n">
         <v>24282</v>
       </c>
-      <c r="C8" s="37" t="inlineStr">
+      <c r="D8" s="34" t="inlineStr">
         <is>
           <t>26/02297</t>
         </is>
       </c>
-      <c r="D8" s="37" t="n"/>
-      <c r="E8" s="37" t="n"/>
-      <c r="F8" s="37" t="n"/>
-      <c r="G8" s="37" t="inlineStr">
+      <c r="E8" s="34" t="n"/>
+      <c r="F8" s="34" t="n"/>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">LABORATORIO TAYUYNA </t>
         </is>
       </c>
-      <c r="H8" s="37" t="inlineStr">
+      <c r="I8" s="34" t="inlineStr">
         <is>
           <t>8,3</t>
         </is>
       </c>
-      <c r="I8" s="37" t="inlineStr">
+      <c r="J8" s="34" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="J8" s="37" t="inlineStr"/>
-      <c r="K8" s="38" t="inlineStr">
+      <c r="K8" s="34" t="inlineStr"/>
+      <c r="L8" s="35" t="inlineStr">
         <is>
           <t>SAI CEDO</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="37" t="inlineStr">
+      <c r="C10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">FAT28136401 </t>
         </is>
       </c>
-      <c r="C10" s="37" t="inlineStr">
+      <c r="D10" s="34" t="inlineStr">
         <is>
           <t>26/02376</t>
         </is>
       </c>
-      <c r="D10" s="37" t="n"/>
-      <c r="E10" s="37" t="n"/>
-      <c r="F10" s="37" t="n"/>
-      <c r="G10" s="37" t="inlineStr">
+      <c r="E10" s="34" t="n"/>
+      <c r="F10" s="34" t="n"/>
+      <c r="G10" s="34" t="n"/>
+      <c r="H10" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve"> CERAMICA ALLEANZA</t>
         </is>
       </c>
-      <c r="H10" s="37" t="inlineStr">
+      <c r="I10" s="34" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I10" s="37" t="inlineStr">
+      <c r="J10" s="34" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J10" s="37" t="inlineStr"/>
-      <c r="K10" s="38" t="inlineStr"/>
+      <c r="K10" s="34" t="inlineStr"/>
+      <c r="L10" s="35" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B1:K2"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="G4:J4"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="F3:F4"/>
-    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="A3:B5"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:L2"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/temporario/ODP_Luis.xlsx
+++ b/temporario/ODP_Luis.xlsx
@@ -6,7 +6,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="16-07-2026_Noite" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Modelo" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="16-07-2026_Noite" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="15-07-2026_Noite" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="14-07-2026_Noite" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -16,8 +19,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -28,7 +31,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="14"/>
@@ -36,33 +38,28 @@
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="10"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="30"/>
       <scheme val="minor"/>
     </font>
     <font>
       <name val="Times New Roman"/>
-      <family val="1"/>
       <b val="1"/>
       <color theme="1"/>
       <sz val="14"/>
     </font>
     <font>
       <name val="Arial"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="14"/>
       <scheme val="minor"/>
@@ -92,7 +89,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -104,6 +101,28 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -114,6 +133,26 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -185,6 +224,24 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -203,10 +260,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
         <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
@@ -275,41 +363,27 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -319,56 +393,98 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -448,6 +564,72 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1428750" cy="571500"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -679,117 +861,113 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA10"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="1.42578125" customWidth="1" min="1" max="1"/>
-    <col width="22.85546875" customWidth="1" min="2" max="2"/>
-    <col width="19.85546875" customWidth="1" min="3" max="3"/>
+    <col width="22.85546875" customWidth="1" min="2" max="3"/>
     <col width="14.85546875" customWidth="1" min="4" max="4"/>
     <col width="17.28515625" customWidth="1" min="5" max="5"/>
     <col width="17.42578125" customWidth="1" min="6" max="6"/>
-    <col width="19.5703125" customWidth="1" min="7" max="7"/>
-    <col width="29.140625" customWidth="1" min="8" max="8"/>
-    <col width="16.42578125" customWidth="1" min="9" max="9"/>
-    <col width="19.85546875" customWidth="1" min="10" max="10"/>
-    <col width="21.5703125" customWidth="1" min="11" max="11"/>
-    <col width="75.7109375" customWidth="1" min="12" max="12"/>
+    <col width="19.85546875" customWidth="1" min="7" max="7"/>
+    <col width="23.28515625" customWidth="1" min="8" max="8"/>
+    <col width="23.85546875" customWidth="1" min="9" max="9"/>
+    <col width="29.140625" customWidth="1" min="10" max="10"/>
+    <col width="16.42578125" customWidth="1" min="11" max="11"/>
+    <col width="19.85546875" customWidth="1" min="12" max="12"/>
+    <col width="21.5703125" customWidth="1" min="13" max="13"/>
+    <col width="75.7109375" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="18" t="n"/>
-      <c r="B1" s="19" t="n"/>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="A1" s="15" t="n"/>
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>ODP´S DE CADA FUNCIONÁRIO</t>
         </is>
       </c>
-      <c r="D1" s="20" t="n"/>
-      <c r="E1" s="20" t="n"/>
-      <c r="F1" s="20" t="n"/>
-      <c r="G1" s="20" t="n"/>
-      <c r="H1" s="20" t="n"/>
-      <c r="I1" s="20" t="n"/>
-      <c r="J1" s="20" t="n"/>
-      <c r="K1" s="20" t="n"/>
-      <c r="L1" s="19" t="n"/>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="29" t="n"/>
+      <c r="G1" s="29" t="n"/>
+      <c r="H1" s="29" t="n"/>
+      <c r="I1" s="29" t="n"/>
+      <c r="J1" s="29" t="n"/>
+      <c r="K1" s="29" t="n"/>
+      <c r="L1" s="29" t="n"/>
+      <c r="M1" s="29" t="n"/>
+      <c r="N1" s="30" t="n"/>
+      <c r="O1" s="6" t="n"/>
     </row>
     <row r="2" ht="58.5" customHeight="1">
-      <c r="A2" s="21" t="n"/>
-      <c r="B2" s="22" t="n"/>
-      <c r="C2" s="21" t="n"/>
-      <c r="D2" s="23" t="n"/>
-      <c r="E2" s="23" t="n"/>
-      <c r="F2" s="23" t="n"/>
-      <c r="G2" s="23" t="n"/>
-      <c r="H2" s="23" t="n"/>
-      <c r="I2" s="23" t="n"/>
-      <c r="J2" s="23" t="n"/>
-      <c r="K2" s="23" t="n"/>
-      <c r="L2" s="22" t="n"/>
+      <c r="A2" s="31" t="n"/>
+      <c r="B2" s="31" t="n"/>
+      <c r="C2" s="32" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="34" t="n"/>
+      <c r="O2" s="6" t="n"/>
     </row>
     <row r="3" ht="29.25" customHeight="1">
-      <c r="A3" s="18" t="n"/>
-      <c r="B3" s="19" t="n"/>
+      <c r="A3" s="35" t="n"/>
+      <c r="B3" s="36" t="n"/>
       <c r="C3" s="7" t="inlineStr">
         <is>
           <t>OPERADOR:</t>
         </is>
       </c>
-      <c r="D3" s="24" t="inlineStr">
-        <is>
-          <t>Luis</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>MÁQUINA:</t>
         </is>
       </c>
-      <c r="F3" s="24" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="F3" s="8" t="n"/>
+      <c r="G3" s="37" t="n"/>
+      <c r="H3" s="29" t="n"/>
+      <c r="I3" s="38" t="n"/>
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>DATA:</t>
         </is>
       </c>
-      <c r="I3" s="26" t="n">
-        <v>46219</v>
-      </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="K3" s="7" t="n"/>
+      <c r="L3" s="7" t="inlineStr">
         <is>
           <t>TURNO:</t>
         </is>
       </c>
-      <c r="K3" s="24" t="inlineStr">
-        <is>
-          <t>Noite</t>
-        </is>
-      </c>
-      <c r="L3" s="9" t="n"/>
+      <c r="M3" s="8" t="n"/>
+      <c r="N3" s="8" t="n"/>
     </row>
     <row r="4" ht="22.5" customHeight="1">
-      <c r="A4" s="27" t="n"/>
-      <c r="B4" s="28" t="n"/>
-      <c r="C4" s="29" t="n"/>
-      <c r="D4" s="30" t="n"/>
-      <c r="E4" s="30" t="n"/>
-      <c r="F4" s="31" t="n"/>
-      <c r="G4" s="32" t="n"/>
-      <c r="H4" s="33" t="n"/>
-      <c r="I4" s="30" t="n"/>
-      <c r="J4" s="30" t="n"/>
-      <c r="K4" s="31" t="n"/>
-      <c r="L4" s="32" t="n"/>
+      <c r="A4" s="39" t="n"/>
+      <c r="B4" s="40" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="44" t="n"/>
+      <c r="H4" s="31" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="41" t="n"/>
+      <c r="K4" s="42" t="n"/>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="43" t="n"/>
+      <c r="N4" s="46" t="n"/>
     </row>
     <row r="5" ht="37.5" customHeight="1">
-      <c r="A5" s="21" t="n"/>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="A5" s="44" t="n"/>
+      <c r="B5" s="45" t="n"/>
+      <c r="C5" s="1" t="inlineStr">
         <is>
           <t>PEDIDO</t>
         </is>
@@ -816,31 +994,39 @@
       </c>
       <c r="H5" s="1" t="inlineStr">
         <is>
+          <t>OP MATERIAL</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>OP TUBETE</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
           <t>CLIENTE</t>
         </is>
       </c>
-      <c r="I5" s="1" t="inlineStr">
+      <c r="K5" s="1" t="inlineStr">
         <is>
           <t>PADRÃO</t>
         </is>
       </c>
-      <c r="J5" s="1" t="inlineStr">
+      <c r="L5" s="1" t="inlineStr">
         <is>
           <t>FILME</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>PESO TUBETE</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>OBS</t>
         </is>
       </c>
-      <c r="M5" s="3" t="n"/>
-      <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="n"/>
       <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="n"/>
@@ -849,123 +1035,938 @@
       <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="n"/>
       <c r="V5" s="3" t="n"/>
-      <c r="W5" s="4" t="n"/>
-      <c r="X5" s="4" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
       <c r="Y5" s="4" t="n"/>
       <c r="Z5" s="4" t="n"/>
       <c r="AA5" s="4" t="n"/>
-    </row>
-    <row r="6" ht="27" customHeight="1">
-      <c r="C6" s="34" t="inlineStr">
-        <is>
-          <t>FAT28210767</t>
-        </is>
-      </c>
-      <c r="D6" s="34" t="inlineStr">
-        <is>
-          <t>26/02408</t>
-        </is>
-      </c>
-      <c r="E6" s="34" t="n"/>
-      <c r="F6" s="34" t="n"/>
-      <c r="G6" s="34" t="n"/>
-      <c r="H6" s="34" t="inlineStr">
-        <is>
-          <t>IZZAPLAST</t>
-        </is>
-      </c>
-      <c r="I6" s="34" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J6" s="34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K6" s="34" t="inlineStr"/>
-      <c r="L6" s="35" t="inlineStr">
-        <is>
-          <t>PESAR BOB, POR BOB, PEDIDO DE UNIDADE / SAI CEDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="C8" s="34" t="n">
-        <v>24282</v>
-      </c>
-      <c r="D8" s="34" t="inlineStr">
-        <is>
-          <t>26/02297</t>
-        </is>
-      </c>
-      <c r="E8" s="34" t="n"/>
-      <c r="F8" s="34" t="n"/>
-      <c r="G8" s="34" t="n"/>
-      <c r="H8" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">LABORATORIO TAYUYNA </t>
-        </is>
-      </c>
-      <c r="I8" s="34" t="inlineStr">
-        <is>
-          <t>8,3</t>
-        </is>
-      </c>
-      <c r="J8" s="34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K8" s="34" t="inlineStr"/>
-      <c r="L8" s="35" t="inlineStr">
-        <is>
-          <t>SAI CEDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="C10" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FAT28136401 </t>
-        </is>
-      </c>
-      <c r="D10" s="34" t="inlineStr">
-        <is>
-          <t>26/02376</t>
-        </is>
-      </c>
-      <c r="E10" s="34" t="n"/>
-      <c r="F10" s="34" t="n"/>
-      <c r="G10" s="34" t="n"/>
-      <c r="H10" s="34" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CERAMICA ALLEANZA</t>
-        </is>
-      </c>
-      <c r="I10" s="34" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J10" s="34" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K10" s="34" t="inlineStr"/>
-      <c r="L10" s="35" t="inlineStr"/>
+      <c r="AB5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="N6" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="H4:K4"/>
     <mergeCell ref="A3:B5"/>
     <mergeCell ref="C4:F4"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="G3:G4"/>
+    <mergeCell ref="C1:N2"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N3:N4"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:L2"/>
+    <mergeCell ref="G3:I4"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC10"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="1.42578125" customWidth="1" min="1" max="1"/>
+    <col width="22.85546875" customWidth="1" min="2" max="3"/>
+    <col width="14.85546875" customWidth="1" min="4" max="4"/>
+    <col width="17.28515625" customWidth="1" min="5" max="5"/>
+    <col width="17.42578125" customWidth="1" min="6" max="6"/>
+    <col width="19.85546875" customWidth="1" min="7" max="7"/>
+    <col width="23.28515625" customWidth="1" min="8" max="8"/>
+    <col width="23.85546875" customWidth="1" min="9" max="9"/>
+    <col width="29.140625" customWidth="1" min="10" max="10"/>
+    <col width="16.42578125" customWidth="1" min="11" max="11"/>
+    <col width="19.85546875" customWidth="1" min="12" max="12"/>
+    <col width="21.5703125" customWidth="1" min="13" max="13"/>
+    <col width="75.7109375" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="15" t="n"/>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>ODP´S DE CADA FUNCIONÁRIO</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="29" t="n"/>
+      <c r="G1" s="29" t="n"/>
+      <c r="H1" s="29" t="n"/>
+      <c r="I1" s="29" t="n"/>
+      <c r="J1" s="29" t="n"/>
+      <c r="K1" s="29" t="n"/>
+      <c r="L1" s="29" t="n"/>
+      <c r="M1" s="29" t="n"/>
+      <c r="N1" s="30" t="n"/>
+      <c r="O1" s="6" t="n"/>
+    </row>
+    <row r="2" ht="58.5" customHeight="1">
+      <c r="A2" s="31" t="n"/>
+      <c r="B2" s="31" t="n"/>
+      <c r="C2" s="32" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="34" t="n"/>
+      <c r="O2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="29.25" customHeight="1">
+      <c r="A3" s="35" t="n"/>
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>OPERADOR:</t>
+        </is>
+      </c>
+      <c r="D3" s="47" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>MÁQUINA:</t>
+        </is>
+      </c>
+      <c r="F3" s="47" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G3" s="37" t="n"/>
+      <c r="H3" s="29" t="n"/>
+      <c r="I3" s="38" t="n"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>DATA:</t>
+        </is>
+      </c>
+      <c r="K3" s="51" t="n">
+        <v>46219</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>TURNO:</t>
+        </is>
+      </c>
+      <c r="M3" s="47" t="inlineStr">
+        <is>
+          <t>Noite</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="39" t="n"/>
+      <c r="B4" s="40" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="44" t="n"/>
+      <c r="H4" s="31" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="41" t="n"/>
+      <c r="K4" s="42" t="n"/>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="43" t="n"/>
+      <c r="N4" s="46" t="n"/>
+    </row>
+    <row r="5" ht="37.5" customHeight="1">
+      <c r="A5" s="44" t="n"/>
+      <c r="B5" s="45" t="n"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>PEDIDO</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>OdP</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Nº do PALETE</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>PESO TOTAL</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>PESO LÍQUIDO</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>OP MATERIAL</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>OP TUBETE</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>CLIENTE</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>PADRÃO</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>FILME</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>PESO TUBETE</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>OBS</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="4" t="n"/>
+      <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n"/>
+      <c r="AB5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>FAT28210767</t>
+        </is>
+      </c>
+      <c r="D6" s="49" t="inlineStr">
+        <is>
+          <t>26/02408</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="49" t="inlineStr">
+        <is>
+          <t>IZZAPLAST</t>
+        </is>
+      </c>
+      <c r="K6" s="49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L6" s="49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M6" s="49" t="inlineStr"/>
+      <c r="N6" s="50" t="inlineStr">
+        <is>
+          <t>PESAR BOB, POR BOB, PEDIDO DE UNIDADE / SAI CEDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="49" t="n">
+        <v>24282</v>
+      </c>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>26/02297</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LABORATORIO TAYUYNA </t>
+        </is>
+      </c>
+      <c r="K8" s="49" t="inlineStr">
+        <is>
+          <t>8,3</t>
+        </is>
+      </c>
+      <c r="L8" s="49" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="M8" s="49" t="inlineStr"/>
+      <c r="N8" s="50" t="inlineStr">
+        <is>
+          <t>SAI CEDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAT28136401 </t>
+        </is>
+      </c>
+      <c r="D10" s="49" t="inlineStr">
+        <is>
+          <t>26/02376</t>
+        </is>
+      </c>
+      <c r="E10" s="49" t="n"/>
+      <c r="F10" s="49" t="n"/>
+      <c r="G10" s="49" t="n"/>
+      <c r="H10" s="49" t="n"/>
+      <c r="I10" s="49" t="n"/>
+      <c r="J10" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> CERAMICA ALLEANZA</t>
+        </is>
+      </c>
+      <c r="K10" s="49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L10" s="49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M10" s="49" t="inlineStr"/>
+      <c r="N10" s="50" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A3:B5"/>
+    <mergeCell ref="C1:N2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="G3:I4"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="1.42578125" customWidth="1" min="1" max="1"/>
+    <col width="22.85546875" customWidth="1" min="2" max="3"/>
+    <col width="14.85546875" customWidth="1" min="4" max="4"/>
+    <col width="17.28515625" customWidth="1" min="5" max="5"/>
+    <col width="17.42578125" customWidth="1" min="6" max="6"/>
+    <col width="19.85546875" customWidth="1" min="7" max="7"/>
+    <col width="23.28515625" customWidth="1" min="8" max="8"/>
+    <col width="23.85546875" customWidth="1" min="9" max="9"/>
+    <col width="29.140625" customWidth="1" min="10" max="10"/>
+    <col width="16.42578125" customWidth="1" min="11" max="11"/>
+    <col width="19.85546875" customWidth="1" min="12" max="12"/>
+    <col width="21.5703125" customWidth="1" min="13" max="13"/>
+    <col width="75.7109375" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="15" t="n"/>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>ODP´S DE CADA FUNCIONÁRIO</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="29" t="n"/>
+      <c r="G1" s="29" t="n"/>
+      <c r="H1" s="29" t="n"/>
+      <c r="I1" s="29" t="n"/>
+      <c r="J1" s="29" t="n"/>
+      <c r="K1" s="29" t="n"/>
+      <c r="L1" s="29" t="n"/>
+      <c r="M1" s="29" t="n"/>
+      <c r="N1" s="30" t="n"/>
+      <c r="O1" s="6" t="n"/>
+    </row>
+    <row r="2" ht="58.5" customHeight="1">
+      <c r="A2" s="31" t="n"/>
+      <c r="B2" s="31" t="n"/>
+      <c r="C2" s="32" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="34" t="n"/>
+      <c r="O2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="29.25" customHeight="1">
+      <c r="A3" s="35" t="n"/>
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>OPERADOR:</t>
+        </is>
+      </c>
+      <c r="D3" s="47" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>MÁQUINA:</t>
+        </is>
+      </c>
+      <c r="F3" s="47" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="G3" s="37" t="n"/>
+      <c r="H3" s="29" t="n"/>
+      <c r="I3" s="38" t="n"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>DATA:</t>
+        </is>
+      </c>
+      <c r="K3" s="51" t="n">
+        <v>46218</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>TURNO:</t>
+        </is>
+      </c>
+      <c r="M3" s="47" t="inlineStr">
+        <is>
+          <t>Noite</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="39" t="n"/>
+      <c r="B4" s="40" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="44" t="n"/>
+      <c r="H4" s="31" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="41" t="n"/>
+      <c r="K4" s="42" t="n"/>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="43" t="n"/>
+      <c r="N4" s="46" t="n"/>
+    </row>
+    <row r="5" ht="37.5" customHeight="1">
+      <c r="A5" s="44" t="n"/>
+      <c r="B5" s="45" t="n"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>PEDIDO</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>OdP</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Nº do PALETE</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>PESO TOTAL</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>PESO LÍQUIDO</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>OP MATERIAL</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>OP TUBETE</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>CLIENTE</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>PADRÃO</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>FILME</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>PESO TUBETE</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>OBS</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="4" t="n"/>
+      <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n"/>
+      <c r="AB5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>FAT27909550</t>
+        </is>
+      </c>
+      <c r="D6" s="49" t="inlineStr">
+        <is>
+          <t>26/02244</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="49" t="inlineStr">
+        <is>
+          <t>FARMABASE</t>
+        </is>
+      </c>
+      <c r="K6" s="49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L6" s="49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M6" s="49" t="inlineStr"/>
+      <c r="N6" s="50" t="inlineStr">
+        <is>
+          <t>COMPLETAR O PEDIDO / SAI CEDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="49" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>26/02257</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="inlineStr">
+        <is>
+          <t>ALFA TRANSPORTES</t>
+        </is>
+      </c>
+      <c r="K8" s="49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L8" s="49" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="M8" s="49" t="inlineStr"/>
+      <c r="N8" s="50" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A3:B5"/>
+    <mergeCell ref="C1:N2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="G3:I4"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AC8"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="1.42578125" customWidth="1" min="1" max="1"/>
+    <col width="22.85546875" customWidth="1" min="2" max="3"/>
+    <col width="14.85546875" customWidth="1" min="4" max="4"/>
+    <col width="17.28515625" customWidth="1" min="5" max="5"/>
+    <col width="17.42578125" customWidth="1" min="6" max="6"/>
+    <col width="19.85546875" customWidth="1" min="7" max="7"/>
+    <col width="23.28515625" customWidth="1" min="8" max="8"/>
+    <col width="23.85546875" customWidth="1" min="9" max="9"/>
+    <col width="29.140625" customWidth="1" min="10" max="10"/>
+    <col width="16.42578125" customWidth="1" min="11" max="11"/>
+    <col width="19.85546875" customWidth="1" min="12" max="12"/>
+    <col width="21.5703125" customWidth="1" min="13" max="13"/>
+    <col width="75.7109375" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="15" t="n"/>
+      <c r="C1" s="22" t="inlineStr">
+        <is>
+          <t>ODP´S DE CADA FUNCIONÁRIO</t>
+        </is>
+      </c>
+      <c r="D1" s="29" t="n"/>
+      <c r="E1" s="29" t="n"/>
+      <c r="F1" s="29" t="n"/>
+      <c r="G1" s="29" t="n"/>
+      <c r="H1" s="29" t="n"/>
+      <c r="I1" s="29" t="n"/>
+      <c r="J1" s="29" t="n"/>
+      <c r="K1" s="29" t="n"/>
+      <c r="L1" s="29" t="n"/>
+      <c r="M1" s="29" t="n"/>
+      <c r="N1" s="30" t="n"/>
+      <c r="O1" s="6" t="n"/>
+    </row>
+    <row r="2" ht="58.5" customHeight="1">
+      <c r="A2" s="31" t="n"/>
+      <c r="B2" s="31" t="n"/>
+      <c r="C2" s="32" t="n"/>
+      <c r="D2" s="33" t="n"/>
+      <c r="E2" s="33" t="n"/>
+      <c r="F2" s="33" t="n"/>
+      <c r="G2" s="33" t="n"/>
+      <c r="H2" s="33" t="n"/>
+      <c r="I2" s="33" t="n"/>
+      <c r="J2" s="33" t="n"/>
+      <c r="K2" s="33" t="n"/>
+      <c r="L2" s="33" t="n"/>
+      <c r="M2" s="33" t="n"/>
+      <c r="N2" s="34" t="n"/>
+      <c r="O2" s="6" t="n"/>
+    </row>
+    <row r="3" ht="29.25" customHeight="1">
+      <c r="A3" s="35" t="n"/>
+      <c r="B3" s="36" t="n"/>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>OPERADOR:</t>
+        </is>
+      </c>
+      <c r="D3" s="47" t="inlineStr">
+        <is>
+          <t>Luis</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>MÁQUINA:</t>
+        </is>
+      </c>
+      <c r="F3" s="47" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G3" s="37" t="n"/>
+      <c r="H3" s="29" t="n"/>
+      <c r="I3" s="38" t="n"/>
+      <c r="J3" s="7" t="inlineStr">
+        <is>
+          <t>DATA:</t>
+        </is>
+      </c>
+      <c r="K3" s="51" t="n">
+        <v>46217</v>
+      </c>
+      <c r="L3" s="7" t="inlineStr">
+        <is>
+          <t>TURNO:</t>
+        </is>
+      </c>
+      <c r="M3" s="47" t="inlineStr">
+        <is>
+          <t>Noite</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="n"/>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="39" t="n"/>
+      <c r="B4" s="40" t="n"/>
+      <c r="C4" s="41" t="n"/>
+      <c r="D4" s="42" t="n"/>
+      <c r="E4" s="42" t="n"/>
+      <c r="F4" s="43" t="n"/>
+      <c r="G4" s="44" t="n"/>
+      <c r="H4" s="31" t="n"/>
+      <c r="I4" s="45" t="n"/>
+      <c r="J4" s="41" t="n"/>
+      <c r="K4" s="42" t="n"/>
+      <c r="L4" s="42" t="n"/>
+      <c r="M4" s="43" t="n"/>
+      <c r="N4" s="46" t="n"/>
+    </row>
+    <row r="5" ht="37.5" customHeight="1">
+      <c r="A5" s="44" t="n"/>
+      <c r="B5" s="45" t="n"/>
+      <c r="C5" s="1" t="inlineStr">
+        <is>
+          <t>PEDIDO</t>
+        </is>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>OdP</t>
+        </is>
+      </c>
+      <c r="E5" s="1" t="inlineStr">
+        <is>
+          <t>Nº do PALETE</t>
+        </is>
+      </c>
+      <c r="F5" s="1" t="inlineStr">
+        <is>
+          <t>PESO TOTAL</t>
+        </is>
+      </c>
+      <c r="G5" s="1" t="inlineStr">
+        <is>
+          <t>PESO LÍQUIDO</t>
+        </is>
+      </c>
+      <c r="H5" s="1" t="inlineStr">
+        <is>
+          <t>OP MATERIAL</t>
+        </is>
+      </c>
+      <c r="I5" s="1" t="inlineStr">
+        <is>
+          <t>OP TUBETE</t>
+        </is>
+      </c>
+      <c r="J5" s="1" t="inlineStr">
+        <is>
+          <t>CLIENTE</t>
+        </is>
+      </c>
+      <c r="K5" s="1" t="inlineStr">
+        <is>
+          <t>PADRÃO</t>
+        </is>
+      </c>
+      <c r="L5" s="1" t="inlineStr">
+        <is>
+          <t>FILME</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>PESO TUBETE</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>OBS</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="n"/>
+      <c r="Q5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
+      <c r="U5" s="3" t="n"/>
+      <c r="V5" s="3" t="n"/>
+      <c r="W5" s="3" t="n"/>
+      <c r="X5" s="3" t="n"/>
+      <c r="Y5" s="4" t="n"/>
+      <c r="Z5" s="4" t="n"/>
+      <c r="AA5" s="4" t="n"/>
+      <c r="AB5" s="4" t="n"/>
+      <c r="AC5" s="4" t="n"/>
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="C6" s="49" t="inlineStr">
+        <is>
+          <t>FAT27192434</t>
+        </is>
+      </c>
+      <c r="D6" s="49" t="inlineStr">
+        <is>
+          <t>26/02293</t>
+        </is>
+      </c>
+      <c r="E6" s="49" t="n"/>
+      <c r="F6" s="49" t="n"/>
+      <c r="G6" s="49" t="n"/>
+      <c r="H6" s="49" t="n"/>
+      <c r="I6" s="49" t="n"/>
+      <c r="J6" s="49" t="inlineStr">
+        <is>
+          <t>YUSEN LOGISTICS 2</t>
+        </is>
+      </c>
+      <c r="K6" s="49" t="inlineStr">
+        <is>
+          <t>3,5 + 0,5</t>
+        </is>
+      </c>
+      <c r="L6" s="49" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M6" s="49" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="N6" s="50" t="inlineStr">
+        <is>
+          <t>COMPLETAR O PALETE / SAI CEDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FAT28122480 </t>
+        </is>
+      </c>
+      <c r="D8" s="49" t="inlineStr">
+        <is>
+          <t>26/02319</t>
+        </is>
+      </c>
+      <c r="E8" s="49" t="n"/>
+      <c r="F8" s="49" t="n"/>
+      <c r="G8" s="49" t="n"/>
+      <c r="H8" s="49" t="n"/>
+      <c r="I8" s="49" t="n"/>
+      <c r="J8" s="49" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> ECOLAB BARUERI</t>
+        </is>
+      </c>
+      <c r="K8" s="49" t="inlineStr">
+        <is>
+          <t>2 + 1,5</t>
+        </is>
+      </c>
+      <c r="L8" s="49" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="M8" s="49" t="inlineStr">
+        <is>
+          <t>1,5</t>
+        </is>
+      </c>
+      <c r="N8" s="50" t="inlineStr">
+        <is>
+          <t>NÃO PASSAR PESO DA BOB, PEDIDO BRUTO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A3:B5"/>
+    <mergeCell ref="C1:N2"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="N3:N4"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="G3:I4"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/temporario/ODP_Luis.xlsx
+++ b/temporario/ODP_Luis.xlsx
@@ -18,9 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -652,6 +651,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom prst="rect"/>
+        <a:ln>
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -1963,8 +1965,8 @@
     <mergeCell ref="A3:B5"/>
     <mergeCell ref="C1:N2"/>
     <mergeCell ref="C4:F4"/>
+    <mergeCell ref="J4:M4"/>
     <mergeCell ref="N3:N4"/>
-    <mergeCell ref="J4:M4"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="G3:I4"/>
   </mergeCells>
